--- a/backend/src/db/demo-docs/measurements-pace-running-shorts.xlsx
+++ b/backend/src/db/demo-docs/measurements-pace-running-shorts.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
@@ -636,6 +636,9 @@
       <c r="G11" s="5" t="n">
         <v>5.08</v>
       </c>
+      <c r="H11" s="5" t="n">
+        <v>5.08</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -650,19 +653,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>63</v>
       </c>
     </row>
@@ -711,19 +717,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>39.5</v>
       </c>
     </row>
@@ -804,19 +813,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>40.5</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>42</v>
       </c>
     </row>
@@ -993,7 +1005,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1006,6 +1018,9 @@
         <v>1.5</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>1.5</v>
       </c>
     </row>
